--- a/Data/ponpeco/Ponpeco Furnitures Sci-Fi - 3610234567/1.6/3610234567.xlsx
+++ b/Data/ponpeco/Ponpeco Furnitures Sci-Fi - 3610234567/1.6/3610234567.xlsx
@@ -2194,7 +2194,7 @@
     <t xml:space="preserve">PFS Artificial Rose</t>
   </si>
   <si>
-    <t xml:space="preserve">PFS 인공 장미 </t>
+    <t xml:space="preserve">PFS 인공 장미</t>
   </si>
   <si>
     <t xml:space="preserve">ThingDef+PFS_DecoTablewareE.description</t>
@@ -2218,7 +2218,7 @@
     <t xml:space="preserve">PFS bedroll</t>
   </si>
   <si>
-    <t xml:space="preserve">PFS 침낭 </t>
+    <t xml:space="preserve">PFS 침낭</t>
   </si>
   <si>
     <t xml:space="preserve">ThingDef+PFS_Bedroll.description</t>
@@ -2230,7 +2230,7 @@
     <t xml:space="preserve">A high-tech bedroll crafted from advanced synthread fibers. Upon activating the air valve, it instantly inflates to provide a level of comfort comparable to a standard bed, even in the middle of a journey. However, it does not seem to improve the actual speed of rest.\nThanks to its specialized structure, it is significantly lighter and more comfortable than a conventional bedroll.\n\nNote: Can only be made of synthread and does not support custom coloring with dye.</t>
   </si>
   <si>
-    <t xml:space="preserve">첨단 신소재 섬유로 제작된 고성능 침낭입니다. 공기 밸브를 작동시키면 즉시 부풀어 올라, 여정 중에도 일반 침대에 버금가는 편안함을 제공합니다. 다만 실제 휴식 속도까지 빨라지는 것 같지는 않습니다.\n특수한 구조 덕분에 일반적인 침낭보다 훨씬 가볍고 편안합니다.\n\n참고: 신소재로만 제작할 수 있으며, 염료를 이용한 색상 변경은 지원하지 않습니다. </t>
+    <t xml:space="preserve">첨단 신소재 섬유로 제작된 고성능 침낭입니다. 공기 밸브를 작동시키면 즉시 부풀어 올라, 여정 중에도 일반 침대에 버금가는 편안함을 제공합니다. 다만 실제 휴식 속도까지 빨라지는 것 같지는 않습니다.\n특수한 구조 덕분에 일반적인 침낭보다 훨씬 가볍고 편안합니다.\n\n참고: 신소재로만 제작할 수 있으며, 염료를 이용한 색상 변경은 지원하지 않습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">A distinctive table formed by combining triangles into a hexagonal shape.
@@ -2348,7 +2348,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2377,16 +2377,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6494,7 +6490,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="25.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="30.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="23.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="67.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="67.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7258,7 +7254,7 @@
       <c r="C45" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="7" t="s">
         <v>674</v>
       </c>
       <c r="F45" s="8" t="s">
@@ -8499,7 +8495,7 @@
       <c r="C118" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="E118" s="9" t="s">
+      <c r="E118" s="7" t="s">
         <v>469</v>
       </c>
       <c r="F118" s="8" t="s">
@@ -8533,7 +8529,7 @@
       <c r="C120" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="E120" s="9" t="s">
+      <c r="E120" s="7" t="s">
         <v>477</v>
       </c>
       <c r="F120" s="8" t="s">
